--- a/conditions.xlsx
+++ b/conditions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60296058-32E8-0142-A4B5-5A78BBD0F021}"/>
   <bookViews>
-    <workbookView xWindow="-41580" yWindow="10000" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25880" yWindow="5600" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/conditions.xlsx
+++ b/conditions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60296058-32E8-0142-A4B5-5A78BBD0F021}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D34928F-6BC8-D348-A5DB-EA77A62028E1}"/>
   <bookViews>
-    <workbookView xWindow="-25880" yWindow="5600" windowWidth="30240" windowHeight="17820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -518,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="15.6640625" customWidth="1"/>
@@ -528,12 +528,12 @@
     <col min="12" max="12" width="16.33203125" customWidth="1"/>
     <col min="13" max="13" width="17.1640625" customWidth="1"/>
     <col min="14" max="14" width="23" customWidth="1"/>
-    <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="21" width="33.33203125" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -579,23 +579,23 @@
       <c r="O1" t="s">
         <v>46</v>
       </c>
+      <c r="P1" t="s">
+        <v>52</v>
+      </c>
       <c r="Q1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s">
-        <v>58</v>
-      </c>
-      <c r="U1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -641,23 +641,23 @@
       <c r="O2" t="s">
         <v>47</v>
       </c>
+      <c r="P2">
+        <v>-6.5000000000000002E-2</v>
+      </c>
       <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>-6.5000000000000002E-2</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
       <c r="S2">
-        <v>-6.5000000000000002E-2</v>
-      </c>
-      <c r="T2">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="U2" t="s">
+      <c r="T2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -697,23 +697,23 @@
       <c r="O3" t="s">
         <v>48</v>
       </c>
+      <c r="P3">
+        <v>-0.03</v>
+      </c>
       <c r="Q3">
+        <v>0.06</v>
+      </c>
+      <c r="R3">
         <v>-0.03</v>
       </c>
-      <c r="R3">
-        <v>0.06</v>
-      </c>
       <c r="S3">
-        <v>-0.03</v>
-      </c>
-      <c r="T3">
         <v>0.05</v>
       </c>
-      <c r="U3" t="s">
+      <c r="T3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -747,20 +747,20 @@
       <c r="N4" t="s">
         <v>51</v>
       </c>
+      <c r="P4">
+        <v>0.03</v>
+      </c>
       <c r="Q4">
+        <v>0.05</v>
+      </c>
+      <c r="R4">
         <v>0.03</v>
       </c>
-      <c r="R4">
-        <v>0.05</v>
-      </c>
       <c r="S4">
-        <v>0.03</v>
-      </c>
-      <c r="T4">
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -791,20 +791,20 @@
       <c r="J5">
         <v>7.4999999999999997E-2</v>
       </c>
+      <c r="P5">
+        <v>6.5000000000000002E-2</v>
+      </c>
       <c r="Q5">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="R5">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="R5">
-        <v>-5.0000000000000001E-3</v>
-      </c>
       <c r="S5">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="T5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -836,7 +836,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -900,7 +900,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>

--- a/conditions.xlsx
+++ b/conditions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D34928F-6BC8-D348-A5DB-EA77A62028E1}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AF02E8-5042-6D43-8AAF-4C8C8A2E685D}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="4520" windowWidth="30240" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -642,7 +642,7 @@
         <v>47</v>
       </c>
       <c r="P2">
-        <v>-6.5000000000000002E-2</v>
+        <v>-0.1313</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>48</v>
       </c>
       <c r="P3">
-        <v>-0.03</v>
+        <v>-4.3799999999999999E-2</v>
       </c>
       <c r="Q3">
         <v>0.06</v>
@@ -748,7 +748,7 @@
         <v>51</v>
       </c>
       <c r="P4">
-        <v>0.03</v>
+        <v>4.3700000000000003E-2</v>
       </c>
       <c r="Q4">
         <v>0.05</v>
@@ -792,7 +792,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="P5">
-        <v>6.5000000000000002E-2</v>
+        <v>0.13120000000000001</v>
       </c>
       <c r="Q5">
         <v>-5.0000000000000001E-3</v>

--- a/conditions.xlsx
+++ b/conditions.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AF02E8-5042-6D43-8AAF-4C8C8A2E685D}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251EB41C-90B9-2C42-9013-E4BE18275E5F}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="4520" windowWidth="30240" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4520" windowWidth="30240" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-6.5000000000000002E-2</v>
+        <v>-0.1313</v>
       </c>
       <c r="S2">
         <v>-5.0000000000000001E-3</v>
@@ -704,7 +704,7 @@
         <v>0.06</v>
       </c>
       <c r="R3">
-        <v>-0.03</v>
+        <v>-4.3799999999999999E-2</v>
       </c>
       <c r="S3">
         <v>0.05</v>
@@ -754,7 +754,7 @@
         <v>0.05</v>
       </c>
       <c r="R4">
-        <v>0.03</v>
+        <v>4.3700000000000003E-2</v>
       </c>
       <c r="S4">
         <v>0.06</v>
@@ -798,7 +798,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
       <c r="R5">
-        <v>6.5000000000000002E-2</v>
+        <v>0.13120000000000001</v>
       </c>
       <c r="S5">
         <v>0</v>

--- a/conditions.xlsx
+++ b/conditions.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251EB41C-90B9-2C42-9013-E4BE18275E5F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{004BF134-E829-A046-BBF2-B0CB2B366CE9}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4520" windowWidth="30240" windowHeight="10220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36800" yWindow="7300" windowWidth="30240" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -524,7 +524,7 @@
     <col min="4" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="16.33203125" customWidth="1"/>
     <col min="13" max="13" width="17.1640625" customWidth="1"/>
     <col min="14" max="14" width="23" customWidth="1"/>

--- a/conditions.xlsx
+++ b/conditions.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{004BF134-E829-A046-BBF2-B0CB2B366CE9}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{F78919DF-FF3E-408A-85B6-348565E8A685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1163EC96-9D43-6143-9A58-78A4C89D7F29}"/>
   <bookViews>
-    <workbookView xWindow="36800" yWindow="7300" windowWidth="30240" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>i</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>Y_pos_rec_rev</t>
+  </si>
+  <si>
+    <t>Downwardchirp</t>
+  </si>
+  <si>
+    <t>Upwardchirp</t>
+  </si>
+  <si>
+    <t>media/downwardchirp.wav</t>
+  </si>
+  <si>
+    <t>media/upwardchirp.wav</t>
   </si>
 </sst>
 </file>
@@ -518,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="15.6640625" customWidth="1"/>
@@ -531,9 +543,10 @@
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="22" customWidth="1"/>
     <col min="20" max="20" width="33.33203125" customWidth="1"/>
+    <col min="21" max="21" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -594,8 +607,14 @@
       <c r="T1" t="s">
         <v>54</v>
       </c>
+      <c r="U1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V1" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -656,8 +675,14 @@
       <c r="T2" t="s">
         <v>55</v>
       </c>
+      <c r="U2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V2" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -713,7 +738,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -760,7 +785,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -804,7 +829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -836,7 +861,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -868,7 +893,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -900,7 +925,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
